--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nokia-my.sharepoint.com/personal/michalis_mochamet_nokia_com/Documents/Documents/italian-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="11_28C60D92FA63FFCD49E8A6975DF45638F2D9E82F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C84CEC91-B26B-4033-8228-5D6E1A19D2E9}"/>
+  <xr:revisionPtr revIDLastSave="240" documentId="11_28C60D92FA63FFCD49E8A6975DF45638F2D9E82F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54EB6558-F407-4D4F-8990-29384F2DA51A}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-12900" yWindow="0" windowWidth="13005" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="574">
   <si>
     <t>Italian</t>
   </si>
@@ -1724,6 +1724,24 @@
   </si>
   <si>
     <t>δεν έχει ήλιο</t>
+  </si>
+  <si>
+    <t>sono stanco, ma vado avanti</t>
+  </si>
+  <si>
+    <t>είμαι κουρασμένος αλλά συνεχίζω</t>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>αλλά</t>
+  </si>
+  <si>
+    <t>chiedere</t>
+  </si>
+  <si>
+    <t>ζητάω</t>
   </si>
 </sst>
 </file>
@@ -2125,7 +2143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D286"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.796875" customWidth="1"/>
@@ -6096,6 +6114,48 @@
         <v>2</v>
       </c>
     </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>568</v>
+      </c>
+      <c r="B284" t="s">
+        <v>569</v>
+      </c>
+      <c r="C284" t="s">
+        <v>504</v>
+      </c>
+      <c r="D284">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>570</v>
+      </c>
+      <c r="B285" t="s">
+        <v>571</v>
+      </c>
+      <c r="C285" t="s">
+        <v>5</v>
+      </c>
+      <c r="D285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>572</v>
+      </c>
+      <c r="B286" t="s">
+        <v>573</v>
+      </c>
+      <c r="C286" t="s">
+        <v>172</v>
+      </c>
+      <c r="D286">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D283">
     <sortCondition ref="A2:A283"/>

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nokia-my.sharepoint.com/personal/michalis_mochamet_nokia_com/Documents/Documents/italian-trainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="11_28C60D92FA63FFCD49E8A6975DF45638F2D9E82F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54EB6558-F407-4D4F-8990-29384F2DA51A}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="11_28C60D92FA63FFCD49E8A6975DF45638F2D9E82F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F202009-537C-4F69-96C7-7EA551662889}"/>
   <bookViews>
-    <workbookView xWindow="-12900" yWindow="0" windowWidth="13005" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="704">
   <si>
     <t>Italian</t>
   </si>
@@ -1742,13 +1742,403 @@
   </si>
   <si>
     <t>ζητάω</t>
+  </si>
+  <si>
+    <t>dove?</t>
+  </si>
+  <si>
+    <t>πού;</t>
+  </si>
+  <si>
+    <t>κατοικείς</t>
+  </si>
+  <si>
+    <t>ποιος(which)</t>
+  </si>
+  <si>
+    <t>palazzo</t>
+  </si>
+  <si>
+    <t>κτήριο</t>
+  </si>
+  <si>
+    <t>appartamento</t>
+  </si>
+  <si>
+    <t>διαμέρισμα</t>
+  </si>
+  <si>
+    <t>si trova</t>
+  </si>
+  <si>
+    <t>βρίσκεται</t>
+  </si>
+  <si>
+    <t>terzo</t>
+  </si>
+  <si>
+    <t>τρίτο</t>
+  </si>
+  <si>
+    <t>piano</t>
+  </si>
+  <si>
+    <t>όροφος</t>
+  </si>
+  <si>
+    <t>vivo</t>
+  </si>
+  <si>
+    <t>sembra</t>
+  </si>
+  <si>
+    <t>φαίνεται</t>
+  </si>
+  <si>
+    <t>nuovo</t>
+  </si>
+  <si>
+    <t>καινούργιος</t>
+  </si>
+  <si>
+    <t>ascensore</t>
+  </si>
+  <si>
+    <t>ανελκυστήρας</t>
+  </si>
+  <si>
+    <t>saliamo</t>
+  </si>
+  <si>
+    <t>ανεβαίνουμε</t>
+  </si>
+  <si>
+    <t>a piedi</t>
+  </si>
+  <si>
+    <t>με τα πόδια</t>
+  </si>
+  <si>
+    <t>purtroppo</t>
+  </si>
+  <si>
+    <t>δυστυχώς</t>
+  </si>
+  <si>
+    <t>rotto</t>
+  </si>
+  <si>
+    <t>χαλασμένος</t>
+  </si>
+  <si>
+    <t>da tempo</t>
+  </si>
+  <si>
+    <t>εδώ και καιρό</t>
+  </si>
+  <si>
+    <t>mi chiamo</t>
+  </si>
+  <si>
+    <t>moglie</t>
+  </si>
+  <si>
+    <t>η σύζυγος</t>
+  </si>
+  <si>
+    <t>fratello</t>
+  </si>
+  <si>
+    <t>αδελφός</t>
+  </si>
+  <si>
+    <t>minore</t>
+  </si>
+  <si>
+    <t>μικρότερος</t>
+  </si>
+  <si>
+    <t>salve!</t>
+  </si>
+  <si>
+    <t>χαίρετε!</t>
+  </si>
+  <si>
+    <t>piacere!</t>
+  </si>
+  <si>
+    <t>χάρηκα!</t>
+  </si>
+  <si>
+    <t>scusi</t>
+  </si>
+  <si>
+    <t>αδελφή</t>
+  </si>
+  <si>
+    <t>viene</t>
+  </si>
+  <si>
+    <t>έρχεται</t>
+  </si>
+  <si>
+    <t>salutare</t>
+  </si>
+  <si>
+    <t>χαιρετάω</t>
+  </si>
+  <si>
+    <t>assomiglia</t>
+  </si>
+  <si>
+    <t>μοιάζει</t>
+  </si>
+  <si>
+    <t>quel</t>
+  </si>
+  <si>
+    <t>εκείνος</t>
+  </si>
+  <si>
+    <t>il quadro</t>
+  </si>
+  <si>
+    <t>κάδρο</t>
+  </si>
+  <si>
+    <t>il muro</t>
+  </si>
+  <si>
+    <t>τοίχος</t>
+  </si>
+  <si>
+    <t>με συγχωρείτε</t>
+  </si>
+  <si>
+    <t>πόσος</t>
+  </si>
+  <si>
+    <t>era</t>
+  </si>
+  <si>
+    <t>ήταν</t>
+  </si>
+  <si>
+    <t>da giovane</t>
+  </si>
+  <si>
+    <t>όταν ήταν νέα</t>
+  </si>
+  <si>
+    <t>μαλλιά</t>
+  </si>
+  <si>
+    <t>μακριά</t>
+  </si>
+  <si>
+    <t>biondi</t>
+  </si>
+  <si>
+    <t>ξανθά</t>
+  </si>
+  <si>
+    <t>lisci</t>
+  </si>
+  <si>
+    <t>ίσια</t>
+  </si>
+  <si>
+    <t>ricci</t>
+  </si>
+  <si>
+    <t>σγουρά</t>
+  </si>
+  <si>
+    <t>mi piacciono</t>
+  </si>
+  <si>
+    <t>μου αρέσουν</t>
+  </si>
+  <si>
+    <t>le caratteristiche</t>
+  </si>
+  <si>
+    <t>χαρακτηριστικά</t>
+  </si>
+  <si>
+    <t>il viso</t>
+  </si>
+  <si>
+    <t>πρόσωπο</t>
+  </si>
+  <si>
+    <t>il naso</t>
+  </si>
+  <si>
+    <t>μύτη</t>
+  </si>
+  <si>
+    <t>naso alla francese</t>
+  </si>
+  <si>
+    <t>γαλλική μύτη</t>
+  </si>
+  <si>
+    <t>gli occhi</t>
+  </si>
+  <si>
+    <t>castani</t>
+  </si>
+  <si>
+    <t>καστανά</t>
+  </si>
+  <si>
+    <t>arrotondati</t>
+  </si>
+  <si>
+    <t>στρογγυλά</t>
+  </si>
+  <si>
+    <t>bocca</t>
+  </si>
+  <si>
+    <t>στόμα</t>
+  </si>
+  <si>
+    <t>bassa</t>
+  </si>
+  <si>
+    <t>κοντή</t>
+  </si>
+  <si>
+    <t>grassa</t>
+  </si>
+  <si>
+    <t>χοντρή</t>
+  </si>
+  <si>
+    <t>riconosci</t>
+  </si>
+  <si>
+    <t>αναγνωρίζεις</t>
+  </si>
+  <si>
+    <t>subito</t>
+  </si>
+  <si>
+    <t>αμέσως</t>
+  </si>
+  <si>
+    <t>piuttosto</t>
+  </si>
+  <si>
+    <t>κάπως</t>
+  </si>
+  <si>
+    <t>magra</t>
+  </si>
+  <si>
+    <t>αδύνατη</t>
+  </si>
+  <si>
+    <t>eccomi</t>
+  </si>
+  <si>
+    <t>να με</t>
+  </si>
+  <si>
+    <t>ci conosciamo</t>
+  </si>
+  <si>
+    <t>γνωριζόμαστε</t>
+  </si>
+  <si>
+    <t>spero</t>
+  </si>
+  <si>
+    <t>ελπίζω</t>
+  </si>
+  <si>
+    <t>pranzo</t>
+  </si>
+  <si>
+    <t>μεσημεριανό</t>
+  </si>
+  <si>
+    <t>pronto</t>
+  </si>
+  <si>
+    <t>έτοιμος</t>
+  </si>
+  <si>
+    <t>τρώω</t>
+  </si>
+  <si>
+    <t>dessert</t>
+  </si>
+  <si>
+    <t>επιδόρπιο</t>
+  </si>
+  <si>
+    <t>adoro</t>
+  </si>
+  <si>
+    <t>λατρεύω</t>
+  </si>
+  <si>
+    <t>nouns</t>
+  </si>
+  <si>
+    <t>βάζουν</t>
+  </si>
+  <si>
+    <t>di solito</t>
+  </si>
+  <si>
+    <t>συνήθως</t>
+  </si>
+  <si>
+    <t>raffredata</t>
+  </si>
+  <si>
+    <t>κρυωμένη</t>
+  </si>
+  <si>
+    <t>spedire</t>
+  </si>
+  <si>
+    <t>στέλνω</t>
+  </si>
+  <si>
+    <t>occhiali da vista</t>
+  </si>
+  <si>
+    <t>γυαλιά οράσεως</t>
+  </si>
+  <si>
+    <t>occhiali da sole</t>
+  </si>
+  <si>
+    <t>γυαλιά ηλίου</t>
+  </si>
+  <si>
+    <t>primo</t>
+  </si>
+  <si>
+    <t>πρώτος</t>
+  </si>
+  <si>
+    <t>secondo</t>
+  </si>
+  <si>
+    <t>δεύτερος</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1776,6 +2166,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1797,12 +2194,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2143,7 +2543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D286"/>
+  <dimension ref="A1:D360"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.796875" customWidth="1"/>
@@ -6156,6 +6556,1042 @@
         <v>2</v>
       </c>
     </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="C287" t="s">
+        <v>8</v>
+      </c>
+      <c r="D287">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="C288" t="s">
+        <v>172</v>
+      </c>
+      <c r="D288">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C289" t="s">
+        <v>8</v>
+      </c>
+      <c r="D289">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C290" t="s">
+        <v>688</v>
+      </c>
+      <c r="D290">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A291" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C291" t="s">
+        <v>688</v>
+      </c>
+      <c r="D291">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="C292" t="s">
+        <v>172</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="C293" t="s">
+        <v>688</v>
+      </c>
+      <c r="D293">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C294" t="s">
+        <v>688</v>
+      </c>
+      <c r="D294">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C295" t="s">
+        <v>688</v>
+      </c>
+      <c r="D295">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C296" t="s">
+        <v>172</v>
+      </c>
+      <c r="D296">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="C297" t="s">
+        <v>172</v>
+      </c>
+      <c r="D297">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="C298" t="s">
+        <v>208</v>
+      </c>
+      <c r="D298">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="C299" t="s">
+        <v>688</v>
+      </c>
+      <c r="D299">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C300" t="s">
+        <v>172</v>
+      </c>
+      <c r="D300">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C301" t="s">
+        <v>208</v>
+      </c>
+      <c r="D301">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="C302" t="s">
+        <v>208</v>
+      </c>
+      <c r="D302">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A303" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C303" t="s">
+        <v>208</v>
+      </c>
+      <c r="D303">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A304" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C304" t="s">
+        <v>504</v>
+      </c>
+      <c r="D304">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A305" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C305" t="s">
+        <v>172</v>
+      </c>
+      <c r="D305">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A306" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="C306" t="s">
+        <v>688</v>
+      </c>
+      <c r="D306">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A307" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C307" t="s">
+        <v>688</v>
+      </c>
+      <c r="D307">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A308" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="C308" t="s">
+        <v>208</v>
+      </c>
+      <c r="D308">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A309" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="C309" t="s">
+        <v>172</v>
+      </c>
+      <c r="D309">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A310" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="C310" t="s">
+        <v>172</v>
+      </c>
+      <c r="D310">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A311" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="C311" t="s">
+        <v>34</v>
+      </c>
+      <c r="D311">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A312" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="C312" t="s">
+        <v>688</v>
+      </c>
+      <c r="D312">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A313" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C313" t="s">
+        <v>34</v>
+      </c>
+      <c r="D313">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A314" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="C314" t="s">
+        <v>172</v>
+      </c>
+      <c r="D314">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A315" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C315" t="s">
+        <v>172</v>
+      </c>
+      <c r="D315">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A316" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="C316" t="s">
+        <v>172</v>
+      </c>
+      <c r="D316">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A317" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="C317" t="s">
+        <v>34</v>
+      </c>
+      <c r="D317">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A318" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="C318" t="s">
+        <v>688</v>
+      </c>
+      <c r="D318">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A319" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="C319" t="s">
+        <v>688</v>
+      </c>
+      <c r="D319">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A320" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="C320" t="s">
+        <v>34</v>
+      </c>
+      <c r="D320">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A321" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="C321" t="s">
+        <v>5</v>
+      </c>
+      <c r="D321">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A322" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C322" t="s">
+        <v>504</v>
+      </c>
+      <c r="D322">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A323" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="C323" t="s">
+        <v>688</v>
+      </c>
+      <c r="D323">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A324" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="C324" t="s">
+        <v>208</v>
+      </c>
+      <c r="D324">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A325" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="C325" t="s">
+        <v>208</v>
+      </c>
+      <c r="D325">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A326" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="C326" t="s">
+        <v>208</v>
+      </c>
+      <c r="D326">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A327" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C327" t="s">
+        <v>5</v>
+      </c>
+      <c r="D327">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A328" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="C328" t="s">
+        <v>208</v>
+      </c>
+      <c r="D328">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A329" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C329" t="s">
+        <v>34</v>
+      </c>
+      <c r="D329">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A330" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="C330" t="s">
+        <v>688</v>
+      </c>
+      <c r="D330">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A331" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="C331" t="s">
+        <v>688</v>
+      </c>
+      <c r="D331">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A332" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="C332" t="s">
+        <v>688</v>
+      </c>
+      <c r="D332">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A333" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C333" t="s">
+        <v>504</v>
+      </c>
+      <c r="D333">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A334" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C334" t="s">
+        <v>688</v>
+      </c>
+      <c r="D334">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A335" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="C335" t="s">
+        <v>208</v>
+      </c>
+      <c r="D335">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A336" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C336" t="s">
+        <v>208</v>
+      </c>
+      <c r="D336">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A337" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C337" t="s">
+        <v>688</v>
+      </c>
+      <c r="D337">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A338" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="C338" t="s">
+        <v>208</v>
+      </c>
+      <c r="D338">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A339" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="C339" t="s">
+        <v>208</v>
+      </c>
+      <c r="D339">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A340" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="C340" t="s">
+        <v>172</v>
+      </c>
+      <c r="D340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A341" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C341" t="s">
+        <v>52</v>
+      </c>
+      <c r="D341">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A342" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C342" t="s">
+        <v>8</v>
+      </c>
+      <c r="D342">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A343" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="C343" t="s">
+        <v>208</v>
+      </c>
+      <c r="D343">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A344" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C344" t="s">
+        <v>5</v>
+      </c>
+      <c r="D344">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A345" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C345" t="s">
+        <v>5</v>
+      </c>
+      <c r="D345">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A346" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="C346" t="s">
+        <v>172</v>
+      </c>
+      <c r="D346">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A347" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C347" t="s">
+        <v>172</v>
+      </c>
+      <c r="D347">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A348" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C348" t="s">
+        <v>688</v>
+      </c>
+      <c r="D348">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A349" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="C349" t="s">
+        <v>208</v>
+      </c>
+      <c r="D349">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A350" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="C350" t="s">
+        <v>172</v>
+      </c>
+      <c r="D350">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A351" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="C351" t="s">
+        <v>688</v>
+      </c>
+      <c r="D351">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A352" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="C352" t="s">
+        <v>172</v>
+      </c>
+      <c r="D352">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A353" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="C353" t="s">
+        <v>172</v>
+      </c>
+      <c r="D353">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A354" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="C354" t="s">
+        <v>34</v>
+      </c>
+      <c r="D354">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A355" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="C355" t="s">
+        <v>34</v>
+      </c>
+      <c r="D355">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A356" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="C356" t="s">
+        <v>172</v>
+      </c>
+      <c r="D356">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A357" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="C357" t="s">
+        <v>504</v>
+      </c>
+      <c r="D357">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A358" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="C358" t="s">
+        <v>504</v>
+      </c>
+      <c r="D358">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A359" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="C359" t="s">
+        <v>208</v>
+      </c>
+      <c r="D359">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A360" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="C360" t="s">
+        <v>208</v>
+      </c>
+      <c r="D360">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D283">
     <sortCondition ref="A2:A283"/>

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19305" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -488,13 +488,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D470"/>
+  <dimension ref="A1:D512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="43.3984375" customWidth="1" min="2" max="2"/>
     <col width="18.8984375" customWidth="1" min="3" max="3"/>
     <col width="14.296875" customWidth="1" min="4" max="4"/>
+    <col width="24.3984375" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9899,7 +9900,848 @@
         <v>3</v>
       </c>
     </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>dai</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>έλα</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Verbs</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>prima</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>πρώτα</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Prepositions</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>dovete lavarvi</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>πρέπει να πλυθείτε</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>le mani</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>χέρια</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>sedermi</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>κάθομαι</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>a tavola</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>στο τραπέζι</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>il cibo</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>φαγητό</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>si raffreda</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>κρυώνει</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>il piatto</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>πιάτο</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>eleganti</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>κομψά</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>usiamo</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>χρησιμοποιώ</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>gli ospiti</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>φιλοξενούμενοι</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>mi ritordo</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>θυμάμαι</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>mai</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>ποτέ</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>si dimentica</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>ξεχνάει</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>sempre</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>πάντα</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>le cose</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>πράγματα</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>scaffale</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>ράφι</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>la sedia</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>καρέρκλα</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>il posto</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>θέση</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>preferito</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>αγαπημένος</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>accanto a</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>δίπλα</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>il vino</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>κρασί</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>sbagliarmi</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>κάνω λάθος</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>forse</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>ίσως</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Adverbs</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>eccoci</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>να ‘μαστε</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>πρώτο πιάτο</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>secondo</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>δεύτερο πιάτο</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Prepositions</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>a parte</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>εκτός από</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>in bianco</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>χωρίς τίποτα</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>buon appetito</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>καλή όρεξη</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>l’antipasto</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>πριν το πρώτο πιάτο</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>la bevanda</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>ποτό</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>mi passi...?</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>μου δίνεις...;</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>l’acqua</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>νερό</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>per favore</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>σε παρακαλώ</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>beviamo</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>πίνουμε</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>mi fermo</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>σταματάω</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>mi sento</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>νιώθω</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>ti alzi</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>σηκώνεσαι</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Phrases</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>vai</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>πήγαινε</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>l’abitudine</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>συνήθεια</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Nouns</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>